--- a/서버정보/20261015_리소스배포_운영.xlsx
+++ b/서버정보/20261015_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CA1ACF-2C2E-4A5D-8902-3A12F651CAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5809533-82DE-43CD-92A2-250D30077E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8311" uniqueCount="1194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8311" uniqueCount="1193">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5761,10 +5761,6 @@
   </si>
   <si>
     <t>PRD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-p-dis-clvap-lb</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -13638,10 +13634,10 @@
         <v>CLV</v>
       </c>
       <c r="D73" s="82" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E73" s="82" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="F73" s="82" t="str">
         <f t="shared" ref="F73:F87" si="34">SUBSTITUTE(E73, "hazr-", "")&amp;"-rule"&amp;O73</f>
@@ -13700,10 +13696,10 @@
         <v>CLV</v>
       </c>
       <c r="D74" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E74" s="74" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="F74" s="74" t="str">
         <f t="shared" si="34"/>
@@ -13762,10 +13758,10 @@
         <v>CLV</v>
       </c>
       <c r="D75" s="82" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E75" s="82" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="F75" s="82" t="str">
         <f t="shared" si="34"/>
@@ -13824,10 +13820,10 @@
         <v>CLV</v>
       </c>
       <c r="D76" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E76" s="74" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="F76" s="74" t="str">
         <f t="shared" si="34"/>
@@ -13886,10 +13882,10 @@
         <v>CLV</v>
       </c>
       <c r="D77" s="82" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E77" s="82" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="F77" s="82" t="str">
         <f t="shared" si="34"/>
@@ -13948,10 +13944,10 @@
         <v>GA</v>
       </c>
       <c r="D78" s="74" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E78" s="74" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="F78" s="74" t="str">
         <f t="shared" si="34"/>
@@ -14010,10 +14006,10 @@
         <v>GA</v>
       </c>
       <c r="D79" s="82" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E79" s="82" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="F79" s="82" t="str">
         <f t="shared" si="34"/>
@@ -27902,19 +27898,19 @@
         <v>CLV</v>
       </c>
       <c r="D148" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E148" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F148" s="82" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G148" s="74" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H148" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I148" s="74">
         <v>4</v>
@@ -27932,7 +27928,7 @@
         <v>991</v>
       </c>
       <c r="N148" s="121" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="O148" s="117" t="str">
         <f t="shared" ref="O148:O157" si="18">SUBSTITUTE(F148,"hazr-","")&amp;"-osdisk"</f>
@@ -27964,7 +27960,7 @@
         <v>345</v>
       </c>
       <c r="Z148" s="95" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="AA148" s="95" t="b">
         <v>1</v>
@@ -27991,19 +27987,19 @@
         <v>CLV</v>
       </c>
       <c r="D149" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E149" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F149" s="74" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G149" s="74" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H149" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I149" s="74">
         <v>4</v>
@@ -28021,7 +28017,7 @@
         <v>991</v>
       </c>
       <c r="N149" s="121" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="O149" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28053,7 +28049,7 @@
         <v>345</v>
       </c>
       <c r="Z149" s="95" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="AA149" s="95" t="b">
         <v>1</v>
@@ -28080,19 +28076,19 @@
         <v>CLV</v>
       </c>
       <c r="D150" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E150" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F150" s="82" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G150" s="74" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H150" s="74" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="I150" s="74">
         <v>4</v>
@@ -28110,7 +28106,7 @@
         <v>991</v>
       </c>
       <c r="N150" s="121" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="O150" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28142,7 +28138,7 @@
         <v>338</v>
       </c>
       <c r="Z150" s="95" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AA150" s="95" t="b">
         <v>1</v>
@@ -28169,19 +28165,19 @@
         <v>CLV</v>
       </c>
       <c r="D151" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E151" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F151" s="74" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G151" s="74" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H151" s="74" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="I151" s="74">
         <v>4</v>
@@ -28199,7 +28195,7 @@
         <v>991</v>
       </c>
       <c r="N151" s="121" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="O151" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28231,7 +28227,7 @@
         <v>338</v>
       </c>
       <c r="Z151" s="95" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AA151" s="95" t="b">
         <v>1</v>
@@ -28258,19 +28254,19 @@
         <v>CLV</v>
       </c>
       <c r="D152" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E152" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F152" s="82" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G152" s="74" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H152" s="74" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="I152" s="74">
         <v>4</v>
@@ -28288,7 +28284,7 @@
         <v>991</v>
       </c>
       <c r="N152" s="121" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="O152" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28320,7 +28316,7 @@
         <v>338</v>
       </c>
       <c r="Z152" s="95" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AA152" s="95" t="b">
         <v>1</v>
@@ -28347,19 +28343,19 @@
         <v>CLV</v>
       </c>
       <c r="D153" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E153" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F153" s="74" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G153" s="74" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H153" s="74" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="I153" s="74">
         <v>4</v>
@@ -28377,7 +28373,7 @@
         <v>991</v>
       </c>
       <c r="N153" s="121" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="O153" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28409,7 +28405,7 @@
         <v>338</v>
       </c>
       <c r="Z153" s="95" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AA153" s="95" t="b">
         <v>1</v>
@@ -28436,19 +28432,19 @@
         <v>CLV</v>
       </c>
       <c r="D154" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E154" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F154" s="82" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G154" s="74" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H154" s="74" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="I154" s="74">
         <v>2</v>
@@ -28466,7 +28462,7 @@
         <v>991</v>
       </c>
       <c r="N154" s="121" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="O154" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28498,7 +28494,7 @@
         <v>338</v>
       </c>
       <c r="Z154" s="95" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AA154" s="95" t="b">
         <v>1</v>
@@ -28525,19 +28521,19 @@
         <v>CLV</v>
       </c>
       <c r="D155" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E155" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F155" s="74" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G155" s="74" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H155" s="74" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="I155" s="74">
         <v>2</v>
@@ -28555,7 +28551,7 @@
         <v>991</v>
       </c>
       <c r="N155" s="121" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="O155" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28587,7 +28583,7 @@
         <v>338</v>
       </c>
       <c r="Z155" s="95" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AA155" s="95" t="b">
         <v>1</v>
@@ -28614,19 +28610,19 @@
         <v>CLV</v>
       </c>
       <c r="D156" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E156" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F156" s="82" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G156" s="74" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H156" s="74" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="I156" s="74">
         <v>4</v>
@@ -28644,7 +28640,7 @@
         <v>991</v>
       </c>
       <c r="N156" s="121" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="O156" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28676,7 +28672,7 @@
         <v>338</v>
       </c>
       <c r="Z156" s="95" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AA156" s="95" t="b">
         <v>1</v>
@@ -28703,19 +28699,19 @@
         <v>CLV</v>
       </c>
       <c r="D157" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E157" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F157" s="95" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G157" s="95" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H157" s="95" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="I157" s="95">
         <v>4</v>
@@ -28733,7 +28729,7 @@
         <v>991</v>
       </c>
       <c r="N157" s="121" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="O157" s="120" t="str">
         <f t="shared" si="18"/>
@@ -28765,7 +28761,7 @@
         <v>338</v>
       </c>
       <c r="Z157" s="95" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AA157" s="95" t="b">
         <v>1</v>
@@ -28798,10 +28794,10 @@
         <v>24</v>
       </c>
       <c r="F158" s="74" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G158" s="74" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H158" s="74" t="s">
         <v>1021</v>
@@ -28822,7 +28818,7 @@
         <v>991</v>
       </c>
       <c r="N158" s="121" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="O158" s="117" t="str">
         <f t="shared" ref="O158:O159" si="20">SUBSTITUTE(F158,"hazr-","")&amp;"-osdisk"</f>
@@ -28887,10 +28883,10 @@
         <v>24</v>
       </c>
       <c r="F159" s="74" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="G159" s="74" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H159" s="74" t="s">
         <v>997</v>
@@ -28911,7 +28907,7 @@
         <v>991</v>
       </c>
       <c r="N159" s="121" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="O159" s="117" t="str">
         <f t="shared" si="20"/>
@@ -28943,7 +28939,7 @@
         <v>338</v>
       </c>
       <c r="Z159" s="95" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="AA159" s="95" t="b">
         <v>1</v>
@@ -28970,19 +28966,19 @@
         <v>GA</v>
       </c>
       <c r="D160" s="74" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E160" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F160" s="74" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G160" s="74" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H160" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I160" s="74">
         <v>4</v>
@@ -29000,7 +28996,7 @@
         <v>991</v>
       </c>
       <c r="N160" s="121" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="O160" s="117" t="str">
         <f>SUBSTITUTE(F160,"hazr-","")&amp;"-osdisk"</f>
@@ -29032,7 +29028,7 @@
         <v>345</v>
       </c>
       <c r="Z160" s="95" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="AA160" s="74" t="b">
         <v>1</v>
@@ -29059,19 +29055,19 @@
         <v>GA</v>
       </c>
       <c r="D161" s="95" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E161" s="95" t="s">
         <v>24</v>
       </c>
       <c r="F161" s="95" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G161" s="95" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H161" s="95" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I161" s="95">
         <v>4</v>
@@ -29089,7 +29085,7 @@
         <v>991</v>
       </c>
       <c r="N161" s="121" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="O161" s="120" t="str">
         <f>SUBSTITUTE(F161,"hazr-","")&amp;"-osdisk"</f>
@@ -29121,7 +29117,7 @@
         <v>345</v>
       </c>
       <c r="Z161" s="95" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="AA161" s="95" t="b">
         <v>1</v>
@@ -29148,16 +29144,16 @@
         <v>GA</v>
       </c>
       <c r="D162" s="95" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E162" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F162" s="95" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G162" s="95" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H162" s="95" t="s">
         <v>997</v>
@@ -29178,7 +29174,7 @@
         <v>991</v>
       </c>
       <c r="N162" s="121" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="O162" s="120" t="str">
         <f>SUBSTITUTE(F162,"hazr-","")&amp;"-osdisk"</f>
@@ -29210,7 +29206,7 @@
         <v>338</v>
       </c>
       <c r="Z162" s="95" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="AA162" s="74" t="b">
         <v>1</v>
@@ -29237,16 +29233,16 @@
         <v>GA</v>
       </c>
       <c r="D163" s="95" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E163" s="95" t="s">
         <v>24</v>
       </c>
       <c r="F163" s="95" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G163" s="95" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H163" s="95" t="s">
         <v>997</v>
@@ -29267,7 +29263,7 @@
         <v>991</v>
       </c>
       <c r="N163" s="121" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="O163" s="120" t="str">
         <f>SUBSTITUTE(F163,"hazr-","")&amp;"-osdisk"</f>
@@ -29299,7 +29295,7 @@
         <v>338</v>
       </c>
       <c r="Z163" s="95" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="AA163" s="95" t="b">
         <v>1</v>
@@ -29326,16 +29322,16 @@
         <v>BSU</v>
       </c>
       <c r="D164" s="95" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="E164" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F164" s="95" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G164" s="95" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H164" s="95" t="s">
         <v>1021</v>
@@ -29353,10 +29349,10 @@
         <v>224</v>
       </c>
       <c r="M164" s="95" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="N164" s="121" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="O164" s="120" t="str">
         <f>SUBSTITUTE(F164,"hazr-","")&amp;"-osdisk"</f>
@@ -29388,7 +29384,7 @@
         <v>338</v>
       </c>
       <c r="Z164" s="95" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="AA164" s="74" t="b">
         <v>1</v>
@@ -37762,13 +37758,13 @@
         <v>CLV</v>
       </c>
       <c r="D157" s="78" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E157" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F157" s="82" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G157" s="73" t="str">
         <f t="shared" si="4"/>
@@ -37817,13 +37813,13 @@
         <v>CLV</v>
       </c>
       <c r="D158" s="80" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E158" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F158" s="74" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G158" s="74" t="str">
         <f t="shared" si="4"/>
@@ -37872,13 +37868,13 @@
         <v>CLV</v>
       </c>
       <c r="D159" s="78" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E159" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F159" s="82" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G159" s="73" t="str">
         <f t="shared" si="4"/>
@@ -37927,13 +37923,13 @@
         <v>CLV</v>
       </c>
       <c r="D160" s="80" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E160" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F160" s="74" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G160" s="74" t="str">
         <f t="shared" si="4"/>
@@ -37982,13 +37978,13 @@
         <v>CLV</v>
       </c>
       <c r="D161" s="78" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E161" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F161" s="82" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G161" s="73" t="str">
         <f t="shared" si="4"/>
@@ -38037,13 +38033,13 @@
         <v>CLV</v>
       </c>
       <c r="D162" s="80" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E162" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F162" s="74" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G162" s="74" t="str">
         <f t="shared" si="4"/>
@@ -38092,13 +38088,13 @@
         <v>CLV</v>
       </c>
       <c r="D163" s="78" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E163" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F163" s="82" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G163" s="73" t="str">
         <f t="shared" si="4"/>
@@ -38147,13 +38143,13 @@
         <v>CLV</v>
       </c>
       <c r="D164" s="80" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E164" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F164" s="74" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G164" s="74" t="str">
         <f t="shared" si="4"/>
@@ -38202,13 +38198,13 @@
         <v>CLV</v>
       </c>
       <c r="D165" s="78" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E165" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F165" s="82" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G165" s="73" t="str">
         <f t="shared" si="4"/>
@@ -38257,13 +38253,13 @@
         <v>CLV</v>
       </c>
       <c r="D166" s="80" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E166" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F166" s="115" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G166" s="74" t="str">
         <f t="shared" si="4"/>
@@ -38318,7 +38314,7 @@
         <v>24</v>
       </c>
       <c r="F167" s="73" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G167" s="73" t="str">
         <f t="shared" ref="G167:G170" si="7">SUBSTITUTE(F167,"hazr-","")&amp;"-disk01"</f>
@@ -38373,7 +38369,7 @@
         <v>24</v>
       </c>
       <c r="F168" s="74" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="G168" s="74" t="str">
         <f t="shared" si="7"/>
@@ -38422,13 +38418,13 @@
         <v>GA</v>
       </c>
       <c r="D169" s="78" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E169" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F169" s="73" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G169" s="73" t="str">
         <f t="shared" si="7"/>
@@ -38477,13 +38473,13 @@
         <v>GA</v>
       </c>
       <c r="D170" s="80" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E170" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F170" s="115" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G170" s="74" t="str">
         <f t="shared" si="7"/>
@@ -38532,13 +38528,13 @@
         <v>GA</v>
       </c>
       <c r="D171" s="78" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E171" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F171" s="114" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G171" s="73" t="str">
         <f t="shared" ref="G171:G173" si="9">SUBSTITUTE(F171,"hazr-","")&amp;"-disk01"</f>
@@ -38587,13 +38583,13 @@
         <v>GA</v>
       </c>
       <c r="D172" s="80" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E172" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F172" s="115" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G172" s="74" t="str">
         <f t="shared" si="9"/>
@@ -38642,13 +38638,13 @@
         <v>BSU</v>
       </c>
       <c r="D173" s="78" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="E173" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F173" s="114" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G173" s="73" t="str">
         <f t="shared" si="9"/>
@@ -43921,7 +43917,7 @@
         <v>233</v>
       </c>
       <c r="H131" s="74" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="I131" s="74"/>
       <c r="J131" s="74"/>
@@ -43954,7 +43950,7 @@
         <v>233</v>
       </c>
       <c r="H132" s="73" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="I132" s="73"/>
       <c r="J132" s="73"/>
@@ -44185,7 +44181,7 @@
         <v>233</v>
       </c>
       <c r="H139" s="74" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="I139" s="74"/>
       <c r="J139" s="74"/>
@@ -44218,7 +44214,7 @@
         <v>233</v>
       </c>
       <c r="H140" s="73" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="I140" s="73"/>
       <c r="J140" s="73"/>
@@ -44443,7 +44439,7 @@
         <v>338</v>
       </c>
       <c r="H147" s="74" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I147" s="74"/>
       <c r="J147" s="74"/>
@@ -44476,7 +44472,7 @@
         <v>233</v>
       </c>
       <c r="H148" s="73" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I148" s="73"/>
       <c r="J148" s="73"/>
@@ -44509,7 +44505,7 @@
         <v>338</v>
       </c>
       <c r="H149" s="74" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="I149" s="74"/>
       <c r="J149" s="74"/>
@@ -44542,7 +44538,7 @@
         <v>233</v>
       </c>
       <c r="H150" s="73" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="I150" s="73"/>
       <c r="J150" s="73"/>
@@ -45331,13 +45327,13 @@
         <v>338</v>
       </c>
       <c r="H170" s="73" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="I170" s="73" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="J170" s="73" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="K170" s="73" t="str">
         <f t="shared" ref="K170:K179" si="10">SUBSTITUTE(I170,"hazr-","")&amp;"-nic"</f>
@@ -45371,13 +45367,13 @@
         <v>338</v>
       </c>
       <c r="H171" s="74" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="I171" s="74" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="J171" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="K171" s="74" t="str">
         <f t="shared" si="10"/>
@@ -45411,13 +45407,13 @@
         <v>338</v>
       </c>
       <c r="H172" s="73" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="I172" s="73" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="J172" s="73" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="K172" s="73" t="str">
         <f t="shared" si="10"/>
@@ -45451,13 +45447,13 @@
         <v>338</v>
       </c>
       <c r="H173" s="74" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="I173" s="74" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="J173" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="K173" s="74" t="str">
         <f t="shared" si="10"/>
@@ -45491,13 +45487,13 @@
         <v>338</v>
       </c>
       <c r="H174" s="73" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="I174" s="73" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="J174" s="73" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="K174" s="73" t="str">
         <f t="shared" si="10"/>
@@ -45531,13 +45527,13 @@
         <v>338</v>
       </c>
       <c r="H175" s="74" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="I175" s="74" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="J175" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="K175" s="74" t="str">
         <f t="shared" si="10"/>
@@ -45571,13 +45567,13 @@
         <v>338</v>
       </c>
       <c r="H176" s="73" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="I176" s="73" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="J176" s="73" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="K176" s="73" t="str">
         <f t="shared" si="10"/>
@@ -45611,13 +45607,13 @@
         <v>338</v>
       </c>
       <c r="H177" s="74" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="I177" s="74" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="J177" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="K177" s="74" t="str">
         <f t="shared" si="10"/>
@@ -45651,13 +45647,13 @@
         <v>338</v>
       </c>
       <c r="H178" s="73" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="I178" s="73" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="J178" s="73" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="K178" s="73" t="str">
         <f t="shared" si="10"/>
@@ -45691,13 +45687,13 @@
         <v>338</v>
       </c>
       <c r="H179" s="74" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="I179" s="74" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="J179" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="K179" s="74" t="str">
         <f t="shared" si="10"/>
@@ -45734,7 +45730,7 @@
         <v>964</v>
       </c>
       <c r="I180" s="73" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="J180" s="73" t="s">
         <v>924</v>
@@ -45771,10 +45767,10 @@
         <v>338</v>
       </c>
       <c r="H181" s="74" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="I181" s="74" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="J181" s="74" t="s">
         <v>924</v>
@@ -45811,13 +45807,13 @@
         <v>345</v>
       </c>
       <c r="H182" s="73" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="I182" s="73" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="J182" s="73" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="K182" s="73" t="str">
         <f t="shared" si="11"/>
@@ -45851,13 +45847,13 @@
         <v>345</v>
       </c>
       <c r="H183" s="74" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="I183" s="74" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="J183" s="74" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="K183" s="74" t="str">
         <f t="shared" si="11"/>
@@ -45891,13 +45887,13 @@
         <v>338</v>
       </c>
       <c r="H184" s="73" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="I184" s="73" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="J184" s="73" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="K184" s="73" t="str">
         <f t="shared" si="11"/>
@@ -45931,13 +45927,13 @@
         <v>338</v>
       </c>
       <c r="H185" s="74" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="I185" s="74" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="J185" s="74" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="K185" s="74" t="str">
         <f t="shared" si="11"/>
@@ -45971,13 +45967,13 @@
         <v>338</v>
       </c>
       <c r="H186" s="73" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="I186" s="73" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="J186" s="73" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="K186" s="73" t="str">
         <f t="shared" si="11"/>
@@ -50891,13 +50887,13 @@
         <v>CLV</v>
       </c>
       <c r="D46" s="82" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E46" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F46" s="82" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="G46" s="82" t="s">
         <v>111</v>
@@ -50906,7 +50902,7 @@
         <v>1015</v>
       </c>
       <c r="I46" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J46" s="82" t="s">
         <v>102</v>
@@ -50916,19 +50912,19 @@
         <v>p-clv-web-lb-fe</v>
       </c>
       <c r="L46" s="82" t="s">
+        <v>1114</v>
+      </c>
+      <c r="M46" s="82" t="s">
         <v>1115</v>
       </c>
-      <c r="M46" s="82" t="s">
-        <v>1116</v>
-      </c>
       <c r="N46" s="82" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="O46" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P46" s="82" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="Q46" s="82" t="str">
         <f t="shared" si="6"/>
@@ -50945,13 +50941,13 @@
         <v>CLV</v>
       </c>
       <c r="D47" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E47" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F47" s="74" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="G47" s="74" t="s">
         <v>111</v>
@@ -50960,7 +50956,7 @@
         <v>1015</v>
       </c>
       <c r="I47" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J47" s="74" t="s">
         <v>102</v>
@@ -50973,16 +50969,16 @@
         <v>317</v>
       </c>
       <c r="M47" s="74" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="N47" s="74" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="O47" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P47" s="74" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="Q47" s="74" t="str">
         <f t="shared" si="6"/>
@@ -50999,13 +50995,13 @@
         <v>CLV</v>
       </c>
       <c r="D48" s="82" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E48" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F48" s="82" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="G48" s="82" t="s">
         <v>111</v>
@@ -51014,7 +51010,7 @@
         <v>1015</v>
       </c>
       <c r="I48" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J48" s="82" t="s">
         <v>102</v>
@@ -51024,19 +51020,19 @@
         <v>p-clv-ssrap-lb-fe</v>
       </c>
       <c r="L48" s="82" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="M48" s="82" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="N48" s="82" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="O48" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P48" s="82" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="Q48" s="82" t="str">
         <f t="shared" si="6"/>
@@ -51053,13 +51049,13 @@
         <v>CLV</v>
       </c>
       <c r="D49" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E49" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F49" s="74" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G49" s="74" t="s">
         <v>111</v>
@@ -51068,7 +51064,7 @@
         <v>1015</v>
       </c>
       <c r="I49" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J49" s="74" t="s">
         <v>102</v>
@@ -51081,16 +51077,16 @@
         <v>317</v>
       </c>
       <c r="M49" s="74" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="N49" s="74" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="O49" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P49" s="74" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="Q49" s="74" t="str">
         <f t="shared" si="6"/>
@@ -51107,13 +51103,13 @@
         <v>CLV</v>
       </c>
       <c r="D50" s="82" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E50" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F50" s="82" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="G50" s="82" t="s">
         <v>111</v>
@@ -51122,7 +51118,7 @@
         <v>1015</v>
       </c>
       <c r="I50" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J50" s="82" t="s">
         <v>102</v>
@@ -51132,19 +51128,19 @@
         <v>p-clv-admap-lb-fe</v>
       </c>
       <c r="L50" s="82" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="M50" s="82" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="N50" s="82" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="O50" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P50" s="82" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="Q50" s="82" t="str">
         <f t="shared" si="6"/>
@@ -51161,13 +51157,13 @@
         <v>GA</v>
       </c>
       <c r="D51" s="74" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E51" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F51" s="74" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="G51" s="74" t="s">
         <v>111</v>
@@ -51176,7 +51172,7 @@
         <v>1015</v>
       </c>
       <c r="I51" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J51" s="74" t="s">
         <v>102</v>
@@ -51192,13 +51188,13 @@
         <v>345</v>
       </c>
       <c r="N51" s="74" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="O51" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P51" s="74" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="Q51" s="74" t="str">
         <f t="shared" si="6"/>
@@ -51215,13 +51211,13 @@
         <v>GA</v>
       </c>
       <c r="D52" s="82" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E52" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F52" s="82" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G52" s="82" t="s">
         <v>111</v>
@@ -51230,7 +51226,7 @@
         <v>1015</v>
       </c>
       <c r="I52" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J52" s="82" t="s">
         <v>102</v>
@@ -51246,13 +51242,13 @@
         <v>338</v>
       </c>
       <c r="N52" s="82" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="O52" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P52" s="82" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="Q52" s="82" t="str">
         <f t="shared" si="6"/>
@@ -53651,17 +53647,17 @@
         <v>CLV</v>
       </c>
       <c r="D73" s="82" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E73" s="82" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="F73" s="82" t="str">
         <f t="shared" si="15"/>
         <v>p-clv-web-lb-pb443</v>
       </c>
       <c r="G73" s="82" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H73" s="82">
         <v>443</v>
@@ -53684,17 +53680,17 @@
         <v>CLV</v>
       </c>
       <c r="D74" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E74" s="74" t="s">
-        <v>1114</v>
+        <v>1192</v>
       </c>
       <c r="F74" s="74" t="str">
         <f t="shared" si="15"/>
-        <v>p-dis-clvap-lb-pb8080</v>
+        <v>p-dis-clv-ap-lb-pb8080</v>
       </c>
       <c r="G74" s="74" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H74" s="74">
         <v>8080</v>
@@ -53717,17 +53713,17 @@
         <v>CLV</v>
       </c>
       <c r="D75" s="82" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E75" s="82" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="F75" s="82" t="str">
         <f t="shared" si="15"/>
         <v>p-clv-ssrap-lb-pb8080</v>
       </c>
       <c r="G75" s="82" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H75" s="82">
         <v>8080</v>
@@ -53750,17 +53746,17 @@
         <v>CLV</v>
       </c>
       <c r="D76" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E76" s="74" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="F76" s="74" t="str">
         <f t="shared" si="15"/>
         <v>p-clv-admweb-lb-pb443</v>
       </c>
       <c r="G76" s="74" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H76" s="74">
         <v>443</v>
@@ -53783,17 +53779,17 @@
         <v>CLV</v>
       </c>
       <c r="D77" s="82" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E77" s="82" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="F77" s="82" t="str">
         <f t="shared" si="15"/>
         <v>p-clv-admap-lb-pb8080</v>
       </c>
       <c r="G77" s="82" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H77" s="82">
         <v>8080</v>
@@ -53816,10 +53812,10 @@
         <v>GA</v>
       </c>
       <c r="D78" s="74" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E78" s="74" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="F78" s="74" t="str">
         <f t="shared" si="15"/>
@@ -53849,10 +53845,10 @@
         <v>GA</v>
       </c>
       <c r="D79" s="82" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E79" s="82" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="F79" s="82" t="str">
         <f t="shared" ref="F79:F87" si="16">SUBSTITUTE(E79, "hazr-", "")&amp;"-pb"&amp;H79</f>
@@ -54143,21 +54139,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -54301,10 +54282,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -54326,19 +54332,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20261015_리소스배포_운영.xlsx
+++ b/서버정보/20261015_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5809533-82DE-43CD-92A2-250D30077E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3113361-A827-4E76-B065-64A485E602C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8311" uniqueCount="1193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8311" uniqueCount="1192">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -6070,10 +6070,6 @@
   </si>
   <si>
     <t>10.158.171.10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-p-dis-clv-ap-lb</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -13699,15 +13695,15 @@
         <v>1122</v>
       </c>
       <c r="E74" s="74" t="s">
-        <v>1192</v>
+        <v>1153</v>
       </c>
       <c r="F74" s="74" t="str">
-        <f t="shared" si="34"/>
-        <v>p-dis-clv-ap-lb-rule8080</v>
+        <f>SUBSTITUTE(E74, "hazr-", "")&amp;"-rule"&amp;O74</f>
+        <v>p-clv-ap-lb-rule8080</v>
       </c>
       <c r="G74" s="74" t="str">
         <f t="shared" si="35"/>
-        <v>p-dis-clv-ap-lb-fe</v>
+        <v>p-clv-ap-lb-fe</v>
       </c>
       <c r="H74" s="74" t="s">
         <v>57</v>
@@ -13720,14 +13716,14 @@
       </c>
       <c r="K74" s="74" t="str">
         <f t="shared" si="36"/>
-        <v>p-dis-clv-ap-lb-bp</v>
+        <v>p-clv-ap-lb-bp</v>
       </c>
       <c r="L74" s="74">
         <v>8080</v>
       </c>
       <c r="M74" s="74" t="str">
         <f t="shared" si="37"/>
-        <v>p-dis-clv-ap-lb-pb8080</v>
+        <v>p-clv-ap-lb-pb8080</v>
       </c>
       <c r="N74" s="74" t="s">
         <v>57</v>
@@ -53683,11 +53679,11 @@
         <v>1122</v>
       </c>
       <c r="E74" s="74" t="s">
-        <v>1192</v>
+        <v>1153</v>
       </c>
       <c r="F74" s="74" t="str">
         <f t="shared" si="15"/>
-        <v>p-dis-clv-ap-lb-pb8080</v>
+        <v>p-clv-ap-lb-pb8080</v>
       </c>
       <c r="G74" s="74" t="s">
         <v>1121</v>
@@ -54139,6 +54135,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -54282,35 +54293,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -54332,9 +54318,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>